--- a/temp_mhr/asignar_plan_53072529.xlsx
+++ b/temp_mhr/asignar_plan_53072529.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700161071</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>501140686</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700160254</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>501139829</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700178805</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>501157670</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700175726</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>501154901</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700180042</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,8473 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>501158917</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>700177311</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>501156216</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>700177680</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>501156585</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>700178492</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>501157357</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>700158121</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>501137986</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>700177004</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>501155899</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>700178130</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>501156995</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>700158115</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>501137980</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>700179117</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>501157982</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>700180033</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>501158908</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>700162521</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>501142226</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>700170982</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>501150067</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>700174724</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>501153879</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>700165633</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>501144628</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>700178131</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>501156996</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>700162036</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>501141711</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>700177642</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>501156547</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>700176148</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>501155323</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>700177903</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>501156808</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>700180031</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>501158906</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>700178790</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>501157665</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>700169345</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>501148400</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>700173532</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>501152667</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>700177331</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>501156236</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>700179115</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>501157980</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>700176043</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>501155218</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>700177902</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>501156807</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>700178223</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>501157088</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>700174712</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>501153857</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>700162386</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>501142091</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>700158789</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>501138633</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>700175725</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>501154900</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>700180073</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>501158938</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>700177895</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>501156800</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>700177304</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>501156209</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>700162041</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>501141716</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>700179218</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>501158083</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>700166265</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>501145260</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>700175777</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>501154952</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>700178275</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>501157140</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>700177987</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>501156842</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>700169346</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>501148401</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>700159761</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>501139673</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>700177069</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>501155967</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>700174593</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>501153748</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>700177309</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>501156214</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>700167137</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>501146142</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>700177307</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>501156212</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>700175758</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>501154933</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>700176946</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>501155841</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>700179533</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>501158408</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>700178505</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>501157370</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>700177731</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>501156636</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>700158786</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>501138630</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>700161461</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>501141076</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>700174384</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>501153529</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>700176289</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>501155484</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>700180030</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>501158905</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>700173255</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>501152380</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>700177638</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>501156543</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>700162384</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>501142089</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>700157674</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>501137509</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>700170514</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>501149589</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>700175759</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>501154934</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>700177681</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>501156586</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>700172035</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>501151140</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>700177322</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>501156227</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>700177464</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>501156369</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>700178806</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>501157671</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>700166080</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>501145085</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>700177918</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>501156823</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>700179574</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>501158449</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>700176947</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>501155842</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>700177721</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>501156626</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>700174723</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>501153878</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>700178230</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>501157095</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>700179708</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>501158583</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>700170082</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>501149147</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>700176118</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>501155293</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>700165716</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>501144721</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>700167283</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>501146298</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>700165628</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>501144623</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>700178788</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>501157663</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>700175794</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>501154959</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>700162040</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>501141715</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>700173939</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>501153074</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>700177003</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>501155898</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>700177916</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>501156821</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
           <t>700161073</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>501140688</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>700163414</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>501143369</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>700177005</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>501155900</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>700178503</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>501157368</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>700178787</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>501157662</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>700162385</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>501142090</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>700162038</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>501141713</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>700166266</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>501145261</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>700162037</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>501141712</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>700179116</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>501157981</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>700179620</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>501158495</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>700167136</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>501146141</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>700177673</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>501156578</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>700177728</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>501156633</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>700161494</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>501141109</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>700178578</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>501157443</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>700174494</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>501153639</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>700176044</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>501155219</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>700156749</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>501136584</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>700160255</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>501139830</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>700178688</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>501157563</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>700156869</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>501136724</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>700177108</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>501156013</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>700177306</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>501156211</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>700175779</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>501154954</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>700077051</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>501035585</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>700177107</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>501156012</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>700175760</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>501154935</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>700175761</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>501154936</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>700177726</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>501156631</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>700177109</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>501156014</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>700167288</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>501146303</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>700177639</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>501156544</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>700163413</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>501143368</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>700157661</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>501137496</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>700170993</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>501150078</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>700177722</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>501156627</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>700177110</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>501156015</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>700179264</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>501158129</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>700162520</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>501142225</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>700172268</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>501151373</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>700176147</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>501155322</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>700177308</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>501156213</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>700169347</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>501148402</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>700174383</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>501153528</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>700161493</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>501141108</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>700157608</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>501137443</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>700179268</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>501158133</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>700163189</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>501143134</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>700159805</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>501139680</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>700178229</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>501157094</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>700172036</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>501151141</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>700156870</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>501136725</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>700179114</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>501157979</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>700173849</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>501152974</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>700161536</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>501141171</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>700157662</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>501137497</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>700176046</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>501155221</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>700177729</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>501156634</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>700177271</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>501156176</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>700157660</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>501137495</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>700174725</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>501153880</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>700178579</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>501157444</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>700177105</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>501156010</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>700178687</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>501157562</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>700175793</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>501154958</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>700178599</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>501157466</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>700172037</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>501151142</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>700178600</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>501157467</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>700165715</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>501144720</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>700161537</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>501141172</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>700177684</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>501156589</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>700176011</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>501155186</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>700175781</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>501154956</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>700156836</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>501136681</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>700166081</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>501145086</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>700170081</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>501149146</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>700167282</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>501146297</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>700178274</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>501157139</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>700168419</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>501147464</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>700176290</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>501155485</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>700176933</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>501155828</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>700173236</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>501152361</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>700180074</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>501158939</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>700173850</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>501152975</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>700162387</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>501142092</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>700168420</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>501147465</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>700178224</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>501157089</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>700177002</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>501155897</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>700175163</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>501154328</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>700177330</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>501156235</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>700161535</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>501141170</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>700177303</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>501156208</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>700175778</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>501154953</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>700167289</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>501146304</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>700173543</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>501152668</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>700177270</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>501156175</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>700176117</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>501155292</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>700172038</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>501151143</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>700177743</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>501156648</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>700157609</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>501137444</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>700177915</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>501156820</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>700179573</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>501158448</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>700177310</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>501156215</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>700158791</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>501138635</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>700158787</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>501138631</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>700158788</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>501138632</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>700177070</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>53074230</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>501155988</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>700172271</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>501151376</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>700165632</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>501144627</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>700173940</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>501153075</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>700158116</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>501137981</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>700161462</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>501141077</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>700179112</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>501157977</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>700176012</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>501155187</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>700178504</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>501157369</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>700172573</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>501151688</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>700178789</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>501157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>700159804</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>501139679</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>700157673</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>501137508</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>700165912</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>501144917</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>700175776</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>501154951</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>700177917</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>501156822</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>700156837</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>501136682</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>700169344</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>501148399</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>700174411</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>501153556</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>700177465</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>501156370</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>700177677</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>501156583</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>700077050</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>501035584</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>700165629</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>501144624</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>700177896</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>501156801</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>700177321</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>501156226</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>700176145</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>501155320</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>700161072</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>501140687</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>700180032</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>501158907</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>700176144</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>501155319</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>700178231</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>501157096</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>700174493</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>501153638</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>700177730</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>501156635</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>700179545</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>501158420</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>700176047</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>501155222</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>700179621</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>501158496</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>700172267</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>501151372</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>700160396</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>501139971</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>700174572</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>501153727</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>700177106</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>501156011</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>700178232</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>501157097</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>700177727</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>501156632</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>700177675</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>501156580</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>700179113</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>501157978</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>700161534</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>501141169</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>700180041</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>501158916</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>700156748</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>501136583</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>700172574</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>501151689</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>700172270</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>501151375</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>700179263</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>501158128</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>700173797</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>501152922</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>700173796</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>501152921</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>700173256</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>501152381</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>700177360</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>501156265</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>700177986</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>501156841</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>700174410</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>53074535</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>501153555</t>
         </is>
       </c>
     </row>

--- a/temp_mhr/asignar_plan_53072529.xlsx
+++ b/temp_mhr/asignar_plan_53072529.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>700161071</t>
+          <t>700179112</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>501140686</t>
+          <t>501157977</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>700160254</t>
+          <t>700172268</t>
         </is>
       </c>
     </row>
@@ -521,14 +521,14 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>501139829</t>
+          <t>501151373</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -572,14 +572,14 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>700175726</t>
+          <t>700177918</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -589,14 +589,14 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501154901</t>
+          <t>501156823</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -606,14 +606,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>700180042</t>
+          <t>700167289</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -623,14 +623,14 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>501158917</t>
+          <t>501146304</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -640,14 +640,14 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>700177311</t>
+          <t>700170982</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -657,14 +657,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>501156216</t>
+          <t>501150067</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>700177680</t>
+          <t>700179264</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -691,14 +691,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>501156585</t>
+          <t>501158129</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>700178492</t>
+          <t>700177681</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -725,14 +725,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>501157357</t>
+          <t>501156586</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700158121</t>
+          <t>700167288</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -759,14 +759,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>501137986</t>
+          <t>501146303</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>700177004</t>
+          <t>700175777</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -793,14 +793,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>501155899</t>
+          <t>501154952</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -810,14 +810,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>700178130</t>
+          <t>700162037</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>501156995</t>
+          <t>501141712</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -844,14 +844,14 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>700158115</t>
+          <t>700161072</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>501137980</t>
+          <t>501140687</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -878,14 +878,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>700179117</t>
+          <t>700161461</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -895,14 +895,14 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>501157982</t>
+          <t>501141076</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -912,14 +912,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>700180033</t>
+          <t>700179573</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -929,14 +929,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>501158908</t>
+          <t>501158448</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>700162521</t>
+          <t>700161536</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -963,14 +963,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>501142226</t>
+          <t>501141171</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>700170982</t>
+          <t>700180031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>501150067</t>
+          <t>501158906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>700174724</t>
+          <t>700169346</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>501153879</t>
+          <t>501148401</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>700165633</t>
+          <t>700174383</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>501144628</t>
+          <t>501153528</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>700178131</t>
+          <t>700174384</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>501156996</t>
+          <t>501153529</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1116,14 +1116,14 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>700162036</t>
+          <t>700177638</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1133,14 +1133,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>501141711</t>
+          <t>501156543</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>700177642</t>
+          <t>700175726</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>501156547</t>
+          <t>501154901</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>700176148</t>
+          <t>700167283</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1201,14 +1201,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>501155323</t>
+          <t>501146298</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1218,14 +1218,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>700177903</t>
+          <t>700179708</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1235,14 +1235,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>501156808</t>
+          <t>501158583</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>700180031</t>
+          <t>700158789</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>501158906</t>
+          <t>501138633</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1286,14 +1286,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>700178790</t>
+          <t>700174493</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>501157665</t>
+          <t>501153638</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1320,14 +1320,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>700169345</t>
+          <t>700177642</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1337,14 +1337,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>501148400</t>
+          <t>501156547</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1354,14 +1354,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>700173532</t>
+          <t>700177270</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>501152667</t>
+          <t>501156175</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1388,14 +1388,14 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>700177331</t>
+          <t>700176289</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>501156236</t>
+          <t>501155484</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>700179115</t>
+          <t>700175776</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>501157980</t>
+          <t>501154951</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1456,14 +1456,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>700176043</t>
+          <t>700177307</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>501155218</t>
+          <t>501156212</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1490,14 +1490,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>700177902</t>
+          <t>700178788</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1507,14 +1507,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>501156807</t>
+          <t>501157663</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>700178223</t>
+          <t>700173255</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>501157088</t>
+          <t>501152380</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>700174712</t>
+          <t>700179620</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,14 +1575,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>501153857</t>
+          <t>501158495</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>700162386</t>
+          <t>700156870</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>501142091</t>
+          <t>501136725</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>700158789</t>
+          <t>700178789</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>501138633</t>
+          <t>501157664</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>700175725</t>
+          <t>700172038</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>501154900</t>
+          <t>501151143</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1694,14 +1694,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>700180073</t>
+          <t>700177108</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>501158938</t>
+          <t>501156013</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1728,14 +1728,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>700177895</t>
+          <t>700177105</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1745,14 +1745,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>501156800</t>
+          <t>501156010</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1762,14 +1762,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>700177304</t>
+          <t>700160254</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>501156209</t>
+          <t>501139829</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>700162041</t>
+          <t>700173850</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1813,14 +1813,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>501141716</t>
+          <t>501152975</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1830,14 +1830,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>700179218</t>
+          <t>700167282</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>501158083</t>
+          <t>501146297</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>700166265</t>
+          <t>700177309</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>501145260</t>
+          <t>501156214</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>700175777</t>
+          <t>700178503</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>501154952</t>
+          <t>501157368</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>700178275</t>
+          <t>700177308</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -1949,14 +1949,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>501157140</t>
+          <t>501156213</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>700177987</t>
+          <t>700167137</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -1983,14 +1983,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>501156842</t>
+          <t>501146142</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>700169346</t>
+          <t>700178578</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>501148401</t>
+          <t>501157443</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>700159761</t>
+          <t>700177004</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2051,14 +2051,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>501139673</t>
+          <t>501155899</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2068,14 +2068,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>700177069</t>
+          <t>700177727</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>501155967</t>
+          <t>501156632</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>700174593</t>
+          <t>700177070</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2119,14 +2119,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>501153748</t>
+          <t>501155988</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>700177309</t>
+          <t>700172574</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2153,14 +2153,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>501156214</t>
+          <t>501151689</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>700167137</t>
+          <t>700177303</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2187,14 +2187,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>501146142</t>
+          <t>501156208</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2204,14 +2204,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>700177307</t>
+          <t>700176946</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2221,14 +2221,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>501156212</t>
+          <t>501155841</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>700175758</t>
+          <t>700162036</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>501154933</t>
+          <t>501141711</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2272,14 +2272,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>700176946</t>
+          <t>700168420</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2289,14 +2289,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>501155841</t>
+          <t>501147465</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>700179533</t>
+          <t>700174593</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2323,14 +2323,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>501158408</t>
+          <t>501153748</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2340,14 +2340,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>700178505</t>
+          <t>700178806</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2357,14 +2357,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>501157370</t>
+          <t>501157671</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>700177731</t>
+          <t>700158786</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2391,14 +2391,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>501156636</t>
+          <t>501138630</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2408,14 +2408,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>700158786</t>
+          <t>700179545</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>501138630</t>
+          <t>501158420</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2442,14 +2442,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>700161461</t>
+          <t>700178579</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2459,14 +2459,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>501141076</t>
+          <t>501157444</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>700174384</t>
+          <t>700177728</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>501153529</t>
+          <t>501156633</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2510,14 +2510,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>700176289</t>
+          <t>700173532</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>501155484</t>
+          <t>501152667</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2544,14 +2544,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>700180030</t>
+          <t>700178275</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>501158905</t>
+          <t>501157140</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2578,14 +2578,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>700173255</t>
+          <t>700174723</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>501152380</t>
+          <t>501153878</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>700177638</t>
+          <t>700172036</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>501156543</t>
+          <t>501151141</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>700157674</t>
+          <t>700174411</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>501137509</t>
+          <t>501153556</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -2714,14 +2714,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>700170514</t>
+          <t>700177673</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>501149589</t>
+          <t>501156578</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>700175759</t>
+          <t>700173796</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>501154934</t>
+          <t>501152921</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>700177681</t>
+          <t>700177684</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>501156586</t>
+          <t>501156589</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>700172035</t>
+          <t>700162520</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -2833,14 +2833,14 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>501151140</t>
+          <t>501142225</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>700177322</t>
+          <t>700180041</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>501156227</t>
+          <t>501158916</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>700177464</t>
+          <t>700158787</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>501156369</t>
+          <t>501138631</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>700178806</t>
+          <t>700177916</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>501157671</t>
+          <t>501156821</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>700166080</t>
+          <t>700177464</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>501145085</t>
+          <t>501156369</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>700177918</t>
+          <t>700176047</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>501156823</t>
+          <t>501155222</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -3020,14 +3020,14 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>700179574</t>
+          <t>700165716</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -3037,14 +3037,14 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>501158449</t>
+          <t>501144721</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -3054,14 +3054,14 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>700176947</t>
+          <t>700156837</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>501155842</t>
+          <t>501136682</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>700177721</t>
+          <t>700161537</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>501156626</t>
+          <t>501141172</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>700174723</t>
+          <t>700177304</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>501153878</t>
+          <t>501156209</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>700178230</t>
+          <t>700160255</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>501157095</t>
+          <t>501139830</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -3190,14 +3190,14 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>700179708</t>
+          <t>700156836</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>501158583</t>
+          <t>501136681</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -3224,14 +3224,14 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>700170082</t>
+          <t>700157662</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -3241,14 +3241,14 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>501149147</t>
+          <t>501137497</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>700176118</t>
+          <t>700170993</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>501155293</t>
+          <t>501150078</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>700165716</t>
+          <t>700178688</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -3309,14 +3309,14 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>501144721</t>
+          <t>501157563</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>700167283</t>
+          <t>700178790</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>501146298</t>
+          <t>501157665</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>700165628</t>
+          <t>700177331</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>501144623</t>
+          <t>501156236</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>700178788</t>
+          <t>700179218</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -3411,14 +3411,14 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>501157663</t>
+          <t>501158083</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -3428,14 +3428,14 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>700175794</t>
+          <t>700157673</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>501154959</t>
+          <t>501137508</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -3462,14 +3462,14 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>700162040</t>
+          <t>700177986</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>501141715</t>
+          <t>501156841</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>700173939</t>
+          <t>700178274</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>501153074</t>
+          <t>501157139</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>700177003</t>
+          <t>700177722</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>501155898</t>
+          <t>501156627</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>700177916</t>
+          <t>700176012</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>501156821</t>
+          <t>501155187</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700178687</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -3615,14 +3615,14 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>501140688</t>
+          <t>501157562</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -3632,14 +3632,14 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>700163414</t>
+          <t>700177987</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -3649,14 +3649,14 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>501143369</t>
+          <t>501156842</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>700177005</t>
+          <t>700180030</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>501155900</t>
+          <t>501158905</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -3700,14 +3700,14 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>700178503</t>
+          <t>700176044</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>501157368</t>
+          <t>501155219</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -3734,14 +3734,14 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>700178787</t>
+          <t>700173797</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>501157662</t>
+          <t>501152922</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>700162385</t>
+          <t>700167136</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>501142090</t>
+          <t>501146141</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>700162038</t>
+          <t>700173939</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>501141713</t>
+          <t>501153074</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -3836,14 +3836,14 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>700166266</t>
+          <t>700177729</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>501145261</t>
+          <t>501156634</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -3870,14 +3870,14 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>700162037</t>
+          <t>700162038</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>501141712</t>
+          <t>501141713</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>700179116</t>
+          <t>700175778</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>501157981</t>
+          <t>501154953</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>700179620</t>
+          <t>700178787</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>501158495</t>
+          <t>501157662</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>700167136</t>
+          <t>700077051</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -3989,14 +3989,14 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>501146141</t>
+          <t>501035585</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -4006,14 +4006,14 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>700177673</t>
+          <t>700176145</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>501156578</t>
+          <t>501155320</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -4040,14 +4040,14 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>700177728</t>
+          <t>700177721</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>501156633</t>
+          <t>501156626</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>700161494</t>
+          <t>700175758</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>501141109</t>
+          <t>501154933</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -4108,14 +4108,14 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>700178578</t>
+          <t>700170514</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -4125,14 +4125,14 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>501157443</t>
+          <t>501149589</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>700174494</t>
+          <t>700175760</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>501153639</t>
+          <t>501154935</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -4176,14 +4176,14 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>700176044</t>
+          <t>700178599</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>501155219</t>
+          <t>501157466</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>700156749</t>
+          <t>700168419</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>501136584</t>
+          <t>501147464</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -4244,14 +4244,14 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>700160255</t>
+          <t>700176933</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>501139830</t>
+          <t>501155828</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>700178688</t>
+          <t>700172267</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -4295,14 +4295,14 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>501157563</t>
+          <t>501151372</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>700156869</t>
+          <t>700159804</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -4329,14 +4329,14 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>501136724</t>
+          <t>501139679</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>700177108</t>
+          <t>700175793</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -4363,14 +4363,14 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>501156013</t>
+          <t>501154958</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>700177306</t>
+          <t>700180032</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>501156211</t>
+          <t>501158907</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -4414,14 +4414,14 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>700175779</t>
+          <t>700175759</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>501154954</t>
+          <t>501154934</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>700077051</t>
+          <t>700170082</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>501035585</t>
+          <t>501149147</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -4482,14 +4482,14 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>700177107</t>
+          <t>700179117</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -4499,14 +4499,14 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>501156012</t>
+          <t>501157982</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>700175760</t>
+          <t>700178504</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>501154935</t>
+          <t>501157369</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -4550,14 +4550,14 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>700175761</t>
+          <t>700162521</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>501154936</t>
+          <t>501142226</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -4584,14 +4584,14 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>700177726</t>
+          <t>700176290</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>501156631</t>
+          <t>501155485</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>700177109</t>
+          <t>700173849</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>501156014</t>
+          <t>501152974</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -4652,14 +4652,14 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>700167288</t>
+          <t>700156869</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>501146303</t>
+          <t>501136724</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -4686,14 +4686,14 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>700177639</t>
+          <t>700177915</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>501156544</t>
+          <t>501156820</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>700163413</t>
+          <t>700180074</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>501143368</t>
+          <t>501158939</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>700157661</t>
+          <t>700172037</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>501137496</t>
+          <t>501151142</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>700170993</t>
+          <t>700179115</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>501150078</t>
+          <t>501157980</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>700177722</t>
+          <t>700163189</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -4839,14 +4839,14 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>501156627</t>
+          <t>501143134</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -4856,14 +4856,14 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>700177110</t>
+          <t>700179113</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>501156015</t>
+          <t>501157978</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -4890,14 +4890,14 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>700179264</t>
+          <t>700177677</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>501158129</t>
+          <t>501156583</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>700162520</t>
+          <t>700180528</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>501142225</t>
+          <t>501159413</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -4958,14 +4958,14 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>700172268</t>
+          <t>700163413</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>501151373</t>
+          <t>501143368</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>700176147</t>
+          <t>700177110</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>501155322</t>
+          <t>501156015</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -5026,14 +5026,14 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>700177308</t>
+          <t>700174494</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -5043,14 +5043,14 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>501156213</t>
+          <t>501153639</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -5060,14 +5060,14 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>700169347</t>
+          <t>700180530</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>501148402</t>
+          <t>501159415</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>700174383</t>
+          <t>700172035</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>501153528</t>
+          <t>501151140</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>700161493</t>
+          <t>700158121</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>501141108</t>
+          <t>501137986</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -5162,14 +5162,14 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>700157608</t>
+          <t>700177003</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -5179,14 +5179,14 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>501137443</t>
+          <t>501155898</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>700179268</t>
+          <t>700177109</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>501158133</t>
+          <t>501156014</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -5230,14 +5230,14 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>700163189</t>
+          <t>700177322</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>501143134</t>
+          <t>501156227</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -5264,14 +5264,14 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>700159805</t>
+          <t>700176043</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -5281,14 +5281,14 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>501139680</t>
+          <t>501155218</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>700178229</t>
+          <t>700170081</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>501157094</t>
+          <t>501149146</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>700172036</t>
+          <t>700176147</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>501151141</t>
+          <t>501155322</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -5366,14 +5366,14 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>700156870</t>
+          <t>700162040</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -5383,14 +5383,14 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>501136725</t>
+          <t>501141715</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5400,14 +5400,14 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>700179114</t>
+          <t>700177002</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>501157979</t>
+          <t>501155897</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>700173849</t>
+          <t>700175779</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -5451,14 +5451,14 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>501152974</t>
+          <t>501154954</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>700161536</t>
+          <t>700178229</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>501141171</t>
+          <t>501157094</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5502,14 +5502,14 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>700157662</t>
+          <t>700180529</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>501137497</t>
+          <t>501159414</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>700176046</t>
+          <t>700174724</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>501155221</t>
+          <t>501153879</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -5570,14 +5570,14 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>700177729</t>
+          <t>700160396</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>501156634</t>
+          <t>501139971</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>700177271</t>
+          <t>700173940</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>501156176</t>
+          <t>501153075</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -5638,14 +5638,14 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>700157660</t>
+          <t>700178223</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -5655,14 +5655,14 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>501137495</t>
+          <t>501157088</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -5672,14 +5672,14 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>700174725</t>
+          <t>700179268</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>501153880</t>
+          <t>501158133</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>700178579</t>
+          <t>700158791</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -5723,14 +5723,14 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>501157444</t>
+          <t>501138635</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -5740,14 +5740,14 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>700177105</t>
+          <t>700157660</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>501156010</t>
+          <t>501137495</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -5774,14 +5774,14 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>700178687</t>
+          <t>700174572</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>501157562</t>
+          <t>501153727</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>700175793</t>
+          <t>700172270</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>501154958</t>
+          <t>501151375</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>700178599</t>
+          <t>700177321</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -5859,14 +5859,14 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>501157466</t>
+          <t>501156226</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>700172037</t>
+          <t>700177731</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>501151142</t>
+          <t>501156636</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>700178600</t>
+          <t>700174725</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -5927,14 +5927,14 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>501157467</t>
+          <t>501153880</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -5944,14 +5944,14 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>700165715</t>
+          <t>700165633</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>501144720</t>
+          <t>501144628</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>700161537</t>
+          <t>700159761</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -5995,14 +5995,14 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>501141172</t>
+          <t>501139673</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>700177684</t>
+          <t>700157661</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -6029,14 +6029,14 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>501156589</t>
+          <t>501137496</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>700176011</t>
+          <t>700166265</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>501155186</t>
+          <t>501145260</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -6080,14 +6080,14 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>700175781</t>
+          <t>700176011</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>501154956</t>
+          <t>501155186</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>700156836</t>
+          <t>700158116</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>501136681</t>
+          <t>501137981</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -6148,14 +6148,14 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>700166081</t>
+          <t>700166080</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -6165,14 +6165,14 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>501145086</t>
+          <t>501145085</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>700170081</t>
+          <t>700163414</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>501149146</t>
+          <t>501143369</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -6216,14 +6216,14 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>700167282</t>
+          <t>700175794</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>501146297</t>
+          <t>501154959</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -6250,14 +6250,14 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>700178274</t>
+          <t>700166266</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -6267,14 +6267,14 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>501157139</t>
+          <t>501145261</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>700168419</t>
+          <t>700174712</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>501147464</t>
+          <t>501153857</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -6318,14 +6318,14 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>700176290</t>
+          <t>700156749</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>501155485</t>
+          <t>501136584</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>700176933</t>
+          <t>700180527</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -6369,14 +6369,14 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>501155828</t>
+          <t>501159412</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>700173236</t>
+          <t>700172573</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>501152361</t>
+          <t>501151688</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>700180074</t>
+          <t>700178224</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>501158939</t>
+          <t>501157089</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -6454,14 +6454,14 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>700173850</t>
+          <t>700177069</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -6471,14 +6471,14 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>501152975</t>
+          <t>501155967</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>700162387</t>
+          <t>700179574</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>501142092</t>
+          <t>501158449</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>700168420</t>
+          <t>700161071</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>501147465</t>
+          <t>501140686</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>700178224</t>
+          <t>700077050</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>501157089</t>
+          <t>501035584</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -6590,14 +6590,14 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>700177002</t>
+          <t>700177730</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>501155897</t>
+          <t>501156635</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>700175163</t>
+          <t>700177271</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -6641,14 +6641,14 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>501154328</t>
+          <t>501156176</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -6658,14 +6658,14 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>700177330</t>
+          <t>700173256</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>501156235</t>
+          <t>501152381</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -6692,14 +6692,14 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>700161535</t>
+          <t>700176117</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -6709,14 +6709,14 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>501141170</t>
+          <t>501155292</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>700177303</t>
+          <t>700157608</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -6743,14 +6743,14 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>501156208</t>
+          <t>501137443</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -6760,14 +6760,14 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>700175778</t>
+          <t>700178130</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>501154953</t>
+          <t>501156995</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>700167289</t>
+          <t>700177675</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>501146304</t>
+          <t>501156580</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -6828,14 +6828,14 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>700173543</t>
+          <t>700161073</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>501152668</t>
+          <t>501140688</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -6862,14 +6862,14 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>700177270</t>
+          <t>700177903</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>501156175</t>
+          <t>501156808</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -6896,14 +6896,14 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>700176117</t>
+          <t>700177306</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -6913,14 +6913,14 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>501155292</t>
+          <t>501156211</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>700172038</t>
+          <t>700179263</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -6947,14 +6947,14 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>501151143</t>
+          <t>501158128</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -6964,14 +6964,14 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>700177743</t>
+          <t>700166081</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>501156648</t>
+          <t>501145086</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>700157609</t>
+          <t>700178505</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>501137444</t>
+          <t>501157370</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>700177915</t>
+          <t>700173543</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>501156820</t>
+          <t>501152668</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -7066,14 +7066,14 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>700179573</t>
+          <t>700161535</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -7083,14 +7083,14 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>501158448</t>
+          <t>501141170</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>700177310</t>
+          <t>700177680</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -7117,14 +7117,14 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>501156215</t>
+          <t>501156585</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>700158791</t>
+          <t>700177310</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>501138635</t>
+          <t>501156215</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -7168,14 +7168,14 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>700158787</t>
+          <t>700178232</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -7185,14 +7185,14 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>501138631</t>
+          <t>501157097</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>700158788</t>
+          <t>700179114</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -7219,14 +7219,14 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>501138632</t>
+          <t>501157979</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -7236,14 +7236,14 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>700177070</t>
+          <t>700161494</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -7253,14 +7253,14 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>501155988</t>
+          <t>501141109</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>700172271</t>
+          <t>700177311</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -7287,14 +7287,14 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>501151376</t>
+          <t>501156216</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -7304,14 +7304,14 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>700165632</t>
+          <t>700158788</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>501144627</t>
+          <t>501138632</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -7338,14 +7338,14 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>700173940</t>
+          <t>700177107</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>501153075</t>
+          <t>501156012</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -7372,14 +7372,14 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>700158116</t>
+          <t>700157609</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>501137981</t>
+          <t>501137444</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -7406,14 +7406,14 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>700161462</t>
+          <t>700162386</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>501141077</t>
+          <t>501142091</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -7440,14 +7440,14 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>700179112</t>
+          <t>700177917</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -7457,14 +7457,14 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>501157977</t>
+          <t>501156822</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>700176012</t>
+          <t>700177005</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>501155187</t>
+          <t>501155900</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -7508,14 +7508,14 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>700178504</t>
+          <t>700177902</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>501157369</t>
+          <t>501156807</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>700172573</t>
+          <t>700175163</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -7559,14 +7559,14 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>501151688</t>
+          <t>501154328</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -7576,14 +7576,14 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>700178789</t>
+          <t>700179116</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>501157664</t>
+          <t>501157981</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -7610,14 +7610,14 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>700159804</t>
+          <t>700156748</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -7627,14 +7627,14 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>501139679</t>
+          <t>501136583</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>700157673</t>
+          <t>700176046</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -7661,14 +7661,14 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>501137508</t>
+          <t>501155221</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -7678,14 +7678,14 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>700165912</t>
+          <t>700177465</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>501144917</t>
+          <t>501156370</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -7712,14 +7712,14 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>700175776</t>
+          <t>700162385</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>501154951</t>
+          <t>501142090</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -7746,14 +7746,14 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>700177917</t>
+          <t>700165715</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>501156822</t>
+          <t>501144720</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -7780,14 +7780,14 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>700156837</t>
+          <t>700162041</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -7797,14 +7797,14 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>501136682</t>
+          <t>501141716</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -7814,14 +7814,14 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>700169344</t>
+          <t>700178492</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>501148399</t>
+          <t>501157357</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -7848,14 +7848,14 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>700174411</t>
+          <t>700175725</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>501153556</t>
+          <t>501154900</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -7882,14 +7882,14 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>700177465</t>
+          <t>700177743</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -7899,14 +7899,14 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>501156370</t>
+          <t>501156648</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -7916,14 +7916,14 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>700177677</t>
+          <t>700176947</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>501156583</t>
+          <t>501155842</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -7950,14 +7950,14 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>700077050</t>
+          <t>700165912</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>501035584</t>
+          <t>501144917</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -7984,14 +7984,14 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>700165629</t>
+          <t>700159805</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -8001,14 +8001,14 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>501144624</t>
+          <t>501139680</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>700177896</t>
+          <t>700180073</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>501156801</t>
+          <t>501158938</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -8052,14 +8052,14 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>700177321</t>
+          <t>700176148</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>501156226</t>
+          <t>501155323</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -8086,14 +8086,14 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>700176145</t>
+          <t>700176144</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -8103,14 +8103,14 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>501155320</t>
+          <t>501155319</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -8120,14 +8120,14 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>700161072</t>
+          <t>700177360</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>501140687</t>
+          <t>501156265</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -8154,14 +8154,14 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>700180032</t>
+          <t>700178231</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -8171,14 +8171,14 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>501158907</t>
+          <t>501157096</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>700176144</t>
+          <t>700176118</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -8205,14 +8205,14 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>501155319</t>
+          <t>501155293</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -8222,14 +8222,14 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>700178231</t>
+          <t>700177330</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>501157096</t>
+          <t>501156235</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>700174493</t>
+          <t>700162387</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -8273,14 +8273,14 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>501153638</t>
+          <t>501142092</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>700177730</t>
+          <t>700177639</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>501156635</t>
+          <t>501156544</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -8324,14 +8324,14 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>700179545</t>
+          <t>700174410</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -8341,14 +8341,14 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>501158420</t>
+          <t>501153555</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -8358,14 +8358,14 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>700176047</t>
+          <t>700161462</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>501155222</t>
+          <t>501141077</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -8392,14 +8392,14 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>700179621</t>
+          <t>700178600</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>501158496</t>
+          <t>501157467</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -8426,14 +8426,14 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>700172267</t>
+          <t>700172271</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -8443,14 +8443,14 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>501151372</t>
+          <t>501151376</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -8460,14 +8460,14 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>700160396</t>
+          <t>700169347</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>501139971</t>
+          <t>501148402</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -8494,14 +8494,14 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>700174572</t>
+          <t>700180033</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>501153727</t>
+          <t>501158908</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>700177106</t>
+          <t>700161534</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -8545,14 +8545,14 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>501156011</t>
+          <t>501141169</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>700178232</t>
+          <t>700157674</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -8579,14 +8579,14 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>501157097</t>
+          <t>501137509</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -8596,14 +8596,14 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>700177727</t>
+          <t>700158115</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -8613,14 +8613,14 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>501156632</t>
+          <t>501137980</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -8630,14 +8630,14 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>700177675</t>
+          <t>700180042</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -8647,14 +8647,14 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>501156580</t>
+          <t>501158917</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -8664,14 +8664,14 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>700179113</t>
+          <t>700165632</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>501157978</t>
+          <t>501144627</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -8698,14 +8698,14 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>700161534</t>
+          <t>700175781</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>501141169</t>
+          <t>501154956</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>700180041</t>
+          <t>700179533</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -8749,14 +8749,14 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>501158916</t>
+          <t>501158408</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -8766,14 +8766,14 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>700156748</t>
+          <t>700177896</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>501136583</t>
+          <t>501156801</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -8800,14 +8800,14 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>700172574</t>
+          <t>700177726</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>501151689</t>
+          <t>501156631</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>700172270</t>
+          <t>700173236</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -8851,14 +8851,14 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>501151375</t>
+          <t>501152361</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -8868,14 +8868,14 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>700179263</t>
+          <t>700175761</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -8885,14 +8885,14 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>501158128</t>
+          <t>501154936</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -8902,14 +8902,14 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>700173797</t>
+          <t>700177106</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -8919,14 +8919,14 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>501152922</t>
+          <t>501156011</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -8936,14 +8936,14 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>700173796</t>
+          <t>700179621</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>501152921</t>
+          <t>501158496</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -8970,14 +8970,14 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>700173256</t>
+          <t>700161493</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>501152381</t>
+          <t>501141108</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>700177360</t>
+          <t>700178230</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>501156265</t>
+          <t>501157095</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>700177986</t>
+          <t>700177895</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>501156841</t>
+          <t>501156800</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -9072,14 +9072,14 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>700174410</t>
+          <t>700178131</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>501153555</t>
+          <t>501156996</t>
         </is>
       </c>
     </row>

--- a/temp_mhr/asignar_plan_53072529.xlsx
+++ b/temp_mhr/asignar_plan_53072529.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C509"/>
+  <dimension ref="A1:C541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -470,14 +470,14 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>700179112</t>
+          <t>700177304</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -487,14 +487,14 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>501157977</t>
+          <t>501156209</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -504,14 +504,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>700172268</t>
+          <t>700179533</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>53074230</t>
+          <t>53074535</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>501151373</t>
+          <t>501158408</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>700178805</t>
+          <t>700180527</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>501157670</t>
+          <t>501159412</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>700177918</t>
+          <t>700176117</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501156823</t>
+          <t>501155292</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>700167289</t>
+          <t>700177722</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>501146304</t>
+          <t>501156627</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>700179264</t>
+          <t>700177309</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>501158129</t>
+          <t>501156214</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>700177681</t>
+          <t>700176012</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>501156586</t>
+          <t>501155187</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700167288</t>
+          <t>700173797</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>501146303</t>
+          <t>501152922</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>700175777</t>
+          <t>700177002</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>501154952</t>
+          <t>501155897</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>700162037</t>
+          <t>700179112</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>501141712</t>
+          <t>501157977</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>700161072</t>
+          <t>700175776</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>501140687</t>
+          <t>501154951</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>700161461</t>
+          <t>700159804</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>501141076</t>
+          <t>501139679</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>700179573</t>
+          <t>700167137</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>501158448</t>
+          <t>501146142</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>700161536</t>
+          <t>700157660</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>501141171</t>
+          <t>501137495</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>700180031</t>
+          <t>700162520</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>501158906</t>
+          <t>501142225</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>700169346</t>
+          <t>700180074</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>501148401</t>
+          <t>501158939</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>700174383</t>
+          <t>700178492</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>501153528</t>
+          <t>501157357</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>700174384</t>
+          <t>700178130</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>501153529</t>
+          <t>501156995</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>700177638</t>
+          <t>700176289</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>501156543</t>
+          <t>501155484</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>700175726</t>
+          <t>700157608</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>501154901</t>
+          <t>501137443</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>700167283</t>
+          <t>700176147</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>501146298</t>
+          <t>501155322</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>700179708</t>
+          <t>700179113</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>501158583</t>
+          <t>501157978</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>700158789</t>
+          <t>700170081</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>501138633</t>
+          <t>501149146</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>700174493</t>
+          <t>700160254</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>501153638</t>
+          <t>501139829</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>700177642</t>
+          <t>700167289</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>501156547</t>
+          <t>501146304</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>700177270</t>
+          <t>700172271</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>501156175</t>
+          <t>501151376</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>700176289</t>
+          <t>700179545</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>501155484</t>
+          <t>501158420</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>700175776</t>
+          <t>700157661</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>501154951</t>
+          <t>501137496</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>700177307</t>
+          <t>700174572</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>501156212</t>
+          <t>501153727</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>700178788</t>
+          <t>700180528</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>501157663</t>
+          <t>501159413</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>700173255</t>
+          <t>700158788</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>501152380</t>
+          <t>501138632</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>700179620</t>
+          <t>700180031</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>501158495</t>
+          <t>501158906</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>700156870</t>
+          <t>700161461</t>
         </is>
       </c>
     </row>
@@ -1609,14 +1609,14 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>501136725</t>
+          <t>501141076</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1626,14 +1626,14 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>700178789</t>
+          <t>700177271</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1643,14 +1643,14 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>501157664</t>
+          <t>501156176</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>700172038</t>
+          <t>700161494</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1677,14 +1677,14 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>501151143</t>
+          <t>501141109</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1694,14 +1694,14 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>700177108</t>
+          <t>700161072</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1711,14 +1711,14 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>501156013</t>
+          <t>501140687</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1728,14 +1728,14 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>700177105</t>
+          <t>700158115</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1745,14 +1745,14 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>501156010</t>
+          <t>501137980</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1762,14 +1762,14 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>700160254</t>
+          <t>700158791</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>501139829</t>
+          <t>501138635</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>700173850</t>
+          <t>700177109</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1813,14 +1813,14 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>501152975</t>
+          <t>501156014</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1830,14 +1830,14 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>700167282</t>
+          <t>700165716</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1847,14 +1847,14 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>501146297</t>
+          <t>501144721</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>700177309</t>
+          <t>700156748</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>501156214</t>
+          <t>501136583</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>700178503</t>
+          <t>700174712</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>501157368</t>
+          <t>501153857</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -1932,14 +1932,14 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>700177308</t>
+          <t>700175759</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -1949,14 +1949,14 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>501156213</t>
+          <t>501154934</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>700167137</t>
+          <t>700180529</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -1983,14 +1983,14 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>501146142</t>
+          <t>501159414</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>700178578</t>
+          <t>700178230</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -2017,14 +2017,14 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>501157443</t>
+          <t>501157095</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -2034,14 +2034,14 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>700177004</t>
+          <t>700176290</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -2051,14 +2051,14 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>501155899</t>
+          <t>501155485</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -2068,14 +2068,14 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>700177727</t>
+          <t>700178788</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -2085,14 +2085,14 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>501156632</t>
+          <t>501157663</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>700177070</t>
+          <t>700179115</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -2119,14 +2119,14 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>501155988</t>
+          <t>501157980</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>700172574</t>
+          <t>700158787</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -2153,14 +2153,14 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>501151689</t>
+          <t>501138631</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -2170,14 +2170,14 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>700177303</t>
+          <t>700173256</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -2187,14 +2187,14 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>501156208</t>
+          <t>501152381</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -2204,14 +2204,14 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>700176946</t>
+          <t>700174593</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -2221,14 +2221,14 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>501155841</t>
+          <t>501153748</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>700162036</t>
+          <t>700161073</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>501141711</t>
+          <t>501140688</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -2272,14 +2272,14 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>700168420</t>
+          <t>700177677</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -2289,14 +2289,14 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>501147465</t>
+          <t>501156583</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>700174593</t>
+          <t>700179218</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -2323,14 +2323,14 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>501153748</t>
+          <t>501158083</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -2340,14 +2340,14 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>700178806</t>
+          <t>700165912</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -2357,14 +2357,14 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>501157671</t>
+          <t>501144917</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>700158786</t>
+          <t>700177465</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -2391,14 +2391,14 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>501138630</t>
+          <t>501156370</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -2408,14 +2408,14 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>700179545</t>
+          <t>700176933</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>501158420</t>
+          <t>501155828</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -2442,14 +2442,14 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>700178579</t>
+          <t>700180395</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -2459,14 +2459,14 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>501157444</t>
+          <t>501159282</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -2476,14 +2476,14 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>700177728</t>
+          <t>700176047</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>501156633</t>
+          <t>501155222</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -2510,14 +2510,14 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>700173532</t>
+          <t>700177105</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>501152667</t>
+          <t>501156010</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -2544,14 +2544,14 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>700178275</t>
+          <t>700167283</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>501157140</t>
+          <t>501146298</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -2578,14 +2578,14 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>700174723</t>
+          <t>700178504</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>501153878</t>
+          <t>501157369</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>700172036</t>
+          <t>700156749</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>501151141</t>
+          <t>501136584</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>700162384</t>
+          <t>700173543</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2663,14 +2663,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>501142089</t>
+          <t>501152668</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>700174411</t>
+          <t>700162387</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>501153556</t>
+          <t>501142092</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -2714,14 +2714,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>700177673</t>
+          <t>700177743</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>501156578</t>
+          <t>501156648</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>700173796</t>
+          <t>700179928</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>501152921</t>
+          <t>501158803</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>700177684</t>
+          <t>700172574</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>501156589</t>
+          <t>501151689</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>700162520</t>
+          <t>700179574</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -2833,14 +2833,14 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>501142225</t>
+          <t>501158449</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>700180041</t>
+          <t>700162384</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>501158916</t>
+          <t>501142089</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>700158787</t>
+          <t>700177681</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>501138631</t>
+          <t>501156586</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>700177916</t>
+          <t>700162385</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>501156821</t>
+          <t>501142090</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>700177464</t>
+          <t>700178599</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>501156369</t>
+          <t>501157466</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>700176047</t>
+          <t>700161462</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>501155222</t>
+          <t>501141077</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -3020,14 +3020,14 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>700165716</t>
+          <t>700077051</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -3037,14 +3037,14 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>501144721</t>
+          <t>501035585</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -3054,14 +3054,14 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>700156837</t>
+          <t>700180725</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>501136682</t>
+          <t>501159620</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>700161537</t>
+          <t>700175794</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>501141172</t>
+          <t>501154959</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>700177304</t>
+          <t>700178505</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>501156209</t>
+          <t>501157370</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>700160255</t>
+          <t>700178503</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>501139830</t>
+          <t>501157368</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -3190,14 +3190,14 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>700156836</t>
+          <t>700177307</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>501136681</t>
+          <t>501156212</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -3224,14 +3224,14 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>700157662</t>
+          <t>700175725</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -3241,14 +3241,14 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>501137497</t>
+          <t>501154900</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>700170993</t>
+          <t>700162037</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>501150078</t>
+          <t>501141712</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>700178688</t>
+          <t>700173796</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -3309,14 +3309,14 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>501157563</t>
+          <t>501152921</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>700178790</t>
+          <t>700163413</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>501157665</t>
+          <t>501143368</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>700177331</t>
+          <t>700179268</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>501156236</t>
+          <t>501158133</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>700179218</t>
+          <t>700167288</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -3411,14 +3411,14 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>501158083</t>
+          <t>501146303</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -3462,14 +3462,14 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>700177986</t>
+          <t>700156869</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>501156841</t>
+          <t>501136724</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>700177722</t>
+          <t>700179117</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>501156627</t>
+          <t>501157982</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>700176012</t>
+          <t>700160255</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>501155187</t>
+          <t>501139830</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>700178687</t>
+          <t>700178579</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -3615,14 +3615,14 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>501157562</t>
+          <t>501157444</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -3632,14 +3632,14 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>700177987</t>
+          <t>700179926</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -3649,14 +3649,14 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>501156842</t>
+          <t>501158801</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>700180030</t>
+          <t>700180687</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>501158905</t>
+          <t>501159572</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -3700,14 +3700,14 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>700176044</t>
+          <t>700177310</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>501155219</t>
+          <t>501156215</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -3734,14 +3734,14 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>700173797</t>
+          <t>700175163</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>501152922</t>
+          <t>501154328</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>700167136</t>
+          <t>700156836</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>501146141</t>
+          <t>501136681</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>700173939</t>
+          <t>700165633</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>501153074</t>
+          <t>501144628</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -3836,14 +3836,14 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>700177729</t>
+          <t>700176011</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>501156634</t>
+          <t>501155186</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -3870,14 +3870,14 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>700162038</t>
+          <t>700177321</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>501141713</t>
+          <t>501156226</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>700175778</t>
+          <t>700169346</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>501154953</t>
+          <t>501148401</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>700178787</t>
+          <t>700172267</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>501157662</t>
+          <t>501151372</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>700077051</t>
+          <t>700177731</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -3989,14 +3989,14 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>501035585</t>
+          <t>501156636</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -4006,14 +4006,14 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>700176145</t>
+          <t>700177004</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>501155320</t>
+          <t>501155899</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -4040,14 +4040,14 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>700177721</t>
+          <t>700172268</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>501156626</t>
+          <t>501151373</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>700175758</t>
+          <t>700179923</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>501154933</t>
+          <t>501158798</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -4108,14 +4108,14 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>700170514</t>
+          <t>700180731</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -4125,14 +4125,14 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>501149589</t>
+          <t>501159626</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>700175760</t>
+          <t>700162036</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -4159,14 +4159,14 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>501154935</t>
+          <t>501141711</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -4176,14 +4176,14 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>700178599</t>
+          <t>700177638</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>501157466</t>
+          <t>501156543</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>700168419</t>
+          <t>700178789</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>501147464</t>
+          <t>501157664</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -4244,14 +4244,14 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>700176933</t>
+          <t>700162386</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>501155828</t>
+          <t>501142091</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>700172267</t>
+          <t>700165715</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -4295,14 +4295,14 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>501151372</t>
+          <t>501144720</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>700159804</t>
+          <t>700180686</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -4329,14 +4329,14 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>501139679</t>
+          <t>501159571</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>700175793</t>
+          <t>700157662</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -4363,14 +4363,14 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>501154958</t>
+          <t>501137497</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>700180032</t>
+          <t>700173255</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>501158907</t>
+          <t>501152380</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -4414,14 +4414,14 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>700175759</t>
+          <t>700176043</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>501154934</t>
+          <t>501155218</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>700170082</t>
+          <t>700180530</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>501149147</t>
+          <t>501159415</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -4482,14 +4482,14 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>700179117</t>
+          <t>700160396</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -4499,14 +4499,14 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>501157982</t>
+          <t>501139971</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>700178504</t>
+          <t>700176044</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>501157369</t>
+          <t>501155219</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -4550,14 +4550,14 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>700162521</t>
+          <t>700179925</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>501142226</t>
+          <t>501158800</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -4584,14 +4584,14 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>700176290</t>
+          <t>700174384</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>501155485</t>
+          <t>501153529</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>700173849</t>
+          <t>700177005</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>501152974</t>
+          <t>501155900</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -4652,14 +4652,14 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>700156869</t>
+          <t>700162041</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>501136724</t>
+          <t>501141716</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -4686,14 +4686,14 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>700177915</t>
+          <t>700162038</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>501156820</t>
+          <t>501141713</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>700180074</t>
+          <t>700177360</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>501158939</t>
+          <t>501156265</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>700172037</t>
+          <t>700158789</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>501151142</t>
+          <t>501138633</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>700179115</t>
+          <t>700176046</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>501157980</t>
+          <t>501155221</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>700163189</t>
+          <t>700180030</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -4839,14 +4839,14 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>501143134</t>
+          <t>501158905</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -4856,14 +4856,14 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>700179113</t>
+          <t>700170082</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>501157978</t>
+          <t>501149147</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -4890,14 +4890,14 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>700177677</t>
+          <t>700163414</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>501156583</t>
+          <t>501143369</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>700180528</t>
+          <t>700177987</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>501159413</t>
+          <t>501156842</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -4958,14 +4958,14 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>700163413</t>
+          <t>700180041</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>501143368</t>
+          <t>501158916</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>700177110</t>
+          <t>700180726</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>501156015</t>
+          <t>501159621</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -5026,14 +5026,14 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>700174494</t>
+          <t>700179911</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -5043,14 +5043,14 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>501153639</t>
+          <t>501158786</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -5060,14 +5060,14 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>700180530</t>
+          <t>700172573</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>501159415</t>
+          <t>501151688</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>700172035</t>
+          <t>700178806</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>501151140</t>
+          <t>501157671</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>700158121</t>
+          <t>700177270</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>501137986</t>
+          <t>501156175</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -5162,14 +5162,14 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>700177003</t>
+          <t>700160292</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -5179,14 +5179,14 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>501155898</t>
+          <t>501139867</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>700177109</t>
+          <t>700177330</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>501156014</t>
+          <t>501156235</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -5230,14 +5230,14 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>700177322</t>
+          <t>700178687</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>501156227</t>
+          <t>501157562</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -5264,14 +5264,14 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>700176043</t>
+          <t>700168419</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -5281,14 +5281,14 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>501155218</t>
+          <t>501147464</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>700170081</t>
+          <t>700077050</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>501149146</t>
+          <t>501035584</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>700176147</t>
+          <t>700175758</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>501155322</t>
+          <t>501154933</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -5366,14 +5366,14 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>700162040</t>
+          <t>700177896</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -5383,14 +5383,14 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>501141715</t>
+          <t>501156801</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5400,14 +5400,14 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>700177002</t>
+          <t>700174411</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>501155897</t>
+          <t>501153556</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>700175779</t>
+          <t>700173849</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -5451,14 +5451,14 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>501154954</t>
+          <t>501152974</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>700178229</t>
+          <t>700176947</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>501157094</t>
+          <t>501155842</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5502,14 +5502,14 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>700180529</t>
+          <t>700176148</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>501159414</t>
+          <t>501155323</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>700174724</t>
+          <t>700163189</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>501153879</t>
+          <t>501143134</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -5570,14 +5570,14 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>700160396</t>
+          <t>700178790</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>501139971</t>
+          <t>501157665</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>700173940</t>
+          <t>700177675</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>501153075</t>
+          <t>501156580</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -5638,14 +5638,14 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>700178223</t>
+          <t>700177918</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -5655,14 +5655,14 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>501157088</t>
+          <t>501156823</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -5672,14 +5672,14 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>700179268</t>
+          <t>700177308</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>501158133</t>
+          <t>501156213</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>700158791</t>
+          <t>700172035</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -5723,14 +5723,14 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>501138635</t>
+          <t>501151140</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -5740,14 +5740,14 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>700157660</t>
+          <t>700178229</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>501137495</t>
+          <t>501157094</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -5774,14 +5774,14 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>700174572</t>
+          <t>700161070</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>501153727</t>
+          <t>501140685</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>700172270</t>
+          <t>700166266</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>501151375</t>
+          <t>501145261</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>700177321</t>
+          <t>700177464</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -5859,14 +5859,14 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>501156226</t>
+          <t>501156369</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>700177731</t>
+          <t>700172036</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>501156636</t>
+          <t>501151141</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>700174725</t>
+          <t>700160293</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -5927,14 +5927,14 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>501153880</t>
+          <t>501139868</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -5944,14 +5944,14 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>700165633</t>
+          <t>700167136</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>501144628</t>
+          <t>501146141</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>700159761</t>
+          <t>700174410</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -5995,14 +5995,14 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>501139673</t>
+          <t>501153555</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>700157661</t>
+          <t>700177110</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -6029,14 +6029,14 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>501137496</t>
+          <t>501156015</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>700166265</t>
+          <t>700169347</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>501145260</t>
+          <t>501148402</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -6080,14 +6080,14 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>700176011</t>
+          <t>700179573</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>501155186</t>
+          <t>501158448</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>700158116</t>
+          <t>700170993</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>501137981</t>
+          <t>501150078</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -6148,14 +6148,14 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>700166080</t>
+          <t>700180033</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -6165,14 +6165,14 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>501145085</t>
+          <t>501158908</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>700163414</t>
+          <t>700161071</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>501143369</t>
+          <t>501140686</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -6216,14 +6216,14 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>700175794</t>
+          <t>700156870</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>501154959</t>
+          <t>501136725</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -6250,14 +6250,14 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>700166266</t>
+          <t>700178231</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -6267,14 +6267,14 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>501145261</t>
+          <t>501157096</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>700174712</t>
+          <t>700176118</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>501153857</t>
+          <t>501155293</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -6318,14 +6318,14 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>700156749</t>
+          <t>700158786</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>501136584</t>
+          <t>501138630</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>700180527</t>
+          <t>700179116</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -6369,14 +6369,14 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>501159412</t>
+          <t>501157981</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>700172573</t>
+          <t>700161535</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>501151688</t>
+          <t>501141170</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>700178224</t>
+          <t>700172270</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>501157089</t>
+          <t>501151375</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -6454,14 +6454,14 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>700177069</t>
+          <t>700178805</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -6471,14 +6471,14 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>501155967</t>
+          <t>501157670</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>700179574</t>
+          <t>700175777</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>501158449</t>
+          <t>501154952</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>700161071</t>
+          <t>700178232</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>501140686</t>
+          <t>501157097</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>700077050</t>
+          <t>700170514</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>501035584</t>
+          <t>501149589</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -6590,14 +6590,14 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>700177730</t>
+          <t>700178787</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>501156635</t>
+          <t>501157662</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>700177271</t>
+          <t>700177915</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -6641,14 +6641,14 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>501156176</t>
+          <t>501156820</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -6658,14 +6658,14 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>700173256</t>
+          <t>700177680</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>501152381</t>
+          <t>501156585</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -6692,14 +6692,14 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>700176117</t>
+          <t>700176144</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -6709,14 +6709,14 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>501155292</t>
+          <t>501155319</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>700157608</t>
+          <t>700177902</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -6743,14 +6743,14 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>501137443</t>
+          <t>501156807</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -6760,14 +6760,14 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>700178130</t>
+          <t>700177727</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>501156995</t>
+          <t>501156632</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>700177675</t>
+          <t>700174723</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>501156580</t>
+          <t>501153878</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -6828,14 +6828,14 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700166265</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>501140688</t>
+          <t>501145260</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -6862,14 +6862,14 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>700177903</t>
+          <t>700177916</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>501156808</t>
+          <t>501156821</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -6896,14 +6896,14 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>700177306</t>
+          <t>700174725</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -6913,14 +6913,14 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>501156211</t>
+          <t>501153880</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>700179263</t>
+          <t>700175793</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -6947,14 +6947,14 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>501158128</t>
+          <t>501154958</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -6964,14 +6964,14 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>700166081</t>
+          <t>700168420</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>501145086</t>
+          <t>501147465</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>700178505</t>
+          <t>700177106</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>501157370</t>
+          <t>501156011</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>700173543</t>
+          <t>700179114</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>501152668</t>
+          <t>501157979</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -7066,14 +7066,14 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>700161535</t>
+          <t>700174724</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -7083,14 +7083,14 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>501141170</t>
+          <t>501153879</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>700177680</t>
+          <t>700177730</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>501156585</t>
+          <t>501156635</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>700177310</t>
+          <t>700177311</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>501156215</t>
+          <t>501156216</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>700178232</t>
+          <t>700177986</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>501157097</t>
+          <t>501156841</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>700179114</t>
+          <t>700179263</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>501157979</t>
+          <t>501158128</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>700161494</t>
+          <t>700177322</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>501141109</t>
+          <t>501156227</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>700177311</t>
+          <t>700177306</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>501156216</t>
+          <t>501156211</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>700158788</t>
+          <t>700175778</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>501138632</t>
+          <t>501154953</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>700157609</t>
+          <t>700161534</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>501137444</t>
+          <t>501141169</t>
         </is>
       </c>
     </row>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>700162386</t>
+          <t>700177642</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>501142091</t>
+          <t>501156547</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>700177917</t>
+          <t>700156837</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>501156822</t>
+          <t>501136682</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>700177005</t>
+          <t>700173236</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>501155900</t>
+          <t>501152361</t>
         </is>
       </c>
     </row>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>700177902</t>
+          <t>700174494</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>501156807</t>
+          <t>501153639</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>700175163</t>
+          <t>700166081</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>501154328</t>
+          <t>501145086</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>700179116</t>
+          <t>700173850</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>501157981</t>
+          <t>501152975</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>700156748</t>
+          <t>700178688</t>
         </is>
       </c>
     </row>
@@ -7627,7 +7627,7 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>501136583</t>
+          <t>501157563</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>700176046</t>
+          <t>700175760</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>501155221</t>
+          <t>501154935</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>700177465</t>
+          <t>700177003</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>501156370</t>
+          <t>501155898</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>700162385</t>
+          <t>700159805</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>501142090</t>
+          <t>501139680</t>
         </is>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>700165715</t>
+          <t>700177639</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>501144720</t>
+          <t>501156544</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>700162041</t>
+          <t>700157674</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>501141716</t>
+          <t>501137509</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>700178492</t>
+          <t>700161537</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>501157357</t>
+          <t>501141172</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>700175725</t>
+          <t>700178275</t>
         </is>
       </c>
     </row>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>501154900</t>
+          <t>501157140</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>700177743</t>
+          <t>700162521</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>501156648</t>
+          <t>501142226</t>
         </is>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>700176947</t>
+          <t>700165632</t>
         </is>
       </c>
     </row>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>501155842</t>
+          <t>501144627</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>700165912</t>
+          <t>700177108</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>501144917</t>
+          <t>501156013</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>700159805</t>
+          <t>700177070</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>501139680</t>
+          <t>501155988</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>700180073</t>
+          <t>700175726</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>501158938</t>
+          <t>501154901</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>700176148</t>
+          <t>700177729</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>501155323</t>
+          <t>501156634</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>700176144</t>
+          <t>700174383</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>501155319</t>
+          <t>501153528</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>700177360</t>
+          <t>700177331</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>501156265</t>
+          <t>501156236</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>700178231</t>
+          <t>700179621</t>
         </is>
       </c>
     </row>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>501157096</t>
+          <t>501158496</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>700176118</t>
+          <t>700179924</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>501155293</t>
+          <t>501158799</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>700177330</t>
+          <t>700177726</t>
         </is>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>501156235</t>
+          <t>501156631</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>700162387</t>
+          <t>700177303</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>501142092</t>
+          <t>501156208</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>700177639</t>
+          <t>700176946</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>501156544</t>
+          <t>501155841</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>700174410</t>
+          <t>700180073</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>501153555</t>
+          <t>501158938</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>700161462</t>
+          <t>700177684</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8375,7 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>501141077</t>
+          <t>501156589</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>700178600</t>
+          <t>700178224</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>501157467</t>
+          <t>501157089</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>700172271</t>
+          <t>700179912</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>501151376</t>
+          <t>501158787</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>700169347</t>
+          <t>700178223</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>501148402</t>
+          <t>501157088</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>700180033</t>
+          <t>700179929</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>501158908</t>
+          <t>501158804</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>700161534</t>
+          <t>700177721</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>501141169</t>
+          <t>501156626</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>700157674</t>
+          <t>700178578</t>
         </is>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>501137509</t>
+          <t>501157443</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>700158115</t>
+          <t>700161536</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>501137980</t>
+          <t>501141171</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>700180042</t>
+          <t>700177069</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>501158917</t>
+          <t>501155967</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>700165632</t>
+          <t>700177903</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>501144627</t>
+          <t>501156808</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>700175781</t>
+          <t>700173532</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>501154956</t>
+          <t>501152667</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>700179533</t>
+          <t>700157609</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>501158408</t>
+          <t>501137444</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>700177896</t>
+          <t>700174493</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>501156801</t>
+          <t>501153638</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>700177726</t>
+          <t>700166080</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>501156631</t>
+          <t>501145085</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>700173236</t>
+          <t>700177917</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>501152361</t>
+          <t>501156822</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>700175761</t>
+          <t>700179708</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>501154936</t>
+          <t>501158583</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>700177106</t>
+          <t>700178131</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>501156011</t>
+          <t>501156996</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>700179621</t>
+          <t>700161493</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>501158496</t>
+          <t>501141108</t>
         </is>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>700161493</t>
+          <t>700180596</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>501141108</t>
+          <t>501159491</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>700178230</t>
+          <t>700177673</t>
         </is>
       </c>
     </row>
@@ -9021,14 +9021,14 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>501157095</t>
+          <t>501156578</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -9038,14 +9038,14 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>700177895</t>
+          <t>700172037</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -9055,14 +9055,14 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>501156800</t>
+          <t>501151142</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -9072,14 +9072,14 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>700178131</t>
+          <t>700176145</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -9089,7 +9089,551 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>501156996</t>
+          <t>501155320</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>700175779</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>501154954</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>700179264</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>501158129</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>700167282</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>501146297</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>700180042</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>501158917</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>700177728</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>501156633</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>700159761</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>501139673</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>700158116</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>501137981</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>700172038</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>501151143</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>700175761</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>501154936</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>700177895</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>501156800</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>700158121</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>501137986</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>700175781</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>501154956</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>700178600</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>501157467</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>700180032</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>501158907</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>700179620</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>501158495</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>700162040</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>501141715</t>
         </is>
       </c>
     </row>

--- a/temp_mhr/asignar_plan_53072529.xlsx
+++ b/temp_mhr/asignar_plan_53072529.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C541"/>
+  <dimension ref="A1:C565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>700177304</t>
+          <t>700161073</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>501156209</t>
+          <t>501140688</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>700179533</t>
+          <t>700178687</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>501158408</t>
+          <t>501157562</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>700180527</t>
+          <t>700179113</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>501159412</t>
+          <t>501157978</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>700176117</t>
+          <t>700177903</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>501155292</t>
+          <t>501156808</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>700177722</t>
+          <t>700175725</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>501156627</t>
+          <t>501154900</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>700170982</t>
+          <t>700077051</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>501150067</t>
+          <t>501035585</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>700177309</t>
+          <t>700162520</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>501156214</t>
+          <t>501142225</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>700176012</t>
+          <t>700177069</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>501155187</t>
+          <t>501155967</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>700173797</t>
+          <t>700161462</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>501152922</t>
+          <t>501141077</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>700177002</t>
+          <t>700170514</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>501155897</t>
+          <t>501149589</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>700179112</t>
+          <t>700177464</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>501157977</t>
+          <t>501156369</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>700175776</t>
+          <t>700176933</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>501154951</t>
+          <t>501155828</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>700159804</t>
+          <t>700166265</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>501139679</t>
+          <t>501145260</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>700167137</t>
+          <t>700158789</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>501146142</t>
+          <t>501138633</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>700157660</t>
+          <t>700179929</t>
         </is>
       </c>
     </row>
@@ -963,14 +963,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>501137495</t>
+          <t>501158804</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>700162520</t>
+          <t>700161461</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>501142225</t>
+          <t>501141076</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1014,14 +1014,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>700180074</t>
+          <t>700158121</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1031,14 +1031,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>501158939</t>
+          <t>501137986</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1048,14 +1048,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>700178492</t>
+          <t>700173256</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>501157357</t>
+          <t>501152381</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1082,14 +1082,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>700178130</t>
+          <t>700161072</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1099,14 +1099,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>501156995</t>
+          <t>501140687</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1116,14 +1116,14 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>700176289</t>
+          <t>700167136</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1133,14 +1133,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>501155484</t>
+          <t>501146141</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>700157608</t>
+          <t>700177680</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1167,14 +1167,14 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>501137443</t>
+          <t>501156585</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>700176147</t>
+          <t>700173532</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1201,14 +1201,14 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>501155322</t>
+          <t>501152667</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1218,14 +1218,14 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>700179113</t>
+          <t>700175761</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1235,14 +1235,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>501157978</t>
+          <t>501154936</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1252,14 +1252,14 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>700170081</t>
+          <t>700156836</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>501149146</t>
+          <t>501136681</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -1286,14 +1286,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>700160254</t>
+          <t>700177107</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>501139829</t>
+          <t>501156012</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1320,14 +1320,14 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>700167289</t>
+          <t>700180530</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1337,14 +1337,14 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>501146304</t>
+          <t>501159415</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1354,14 +1354,14 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>700172271</t>
+          <t>700157673</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>501151376</t>
+          <t>501137508</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1388,14 +1388,14 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>700179545</t>
+          <t>700168420</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1405,14 +1405,14 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>501158420</t>
+          <t>501147465</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>700157661</t>
+          <t>700172268</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1439,14 +1439,14 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>501137496</t>
+          <t>501151373</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1456,14 +1456,14 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>700174572</t>
+          <t>700166266</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1473,14 +1473,14 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>501153727</t>
+          <t>501145261</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1490,14 +1490,14 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>700180528</t>
+          <t>700161534</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1507,14 +1507,14 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>501159413</t>
+          <t>501141169</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>700158788</t>
+          <t>700169347</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>501138632</t>
+          <t>501148402</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>700180031</t>
+          <t>700175760</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1575,14 +1575,14 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>501158906</t>
+          <t>501154935</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>700161461</t>
+          <t>700157674</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>53074535</t>
+          <t>53073989</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>501141076</t>
+          <t>501137509</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>700177271</t>
+          <t>700167137</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>501156176</t>
+          <t>501146142</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>700161494</t>
+          <t>700177105</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>501141109</t>
+          <t>501156010</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>700161072</t>
+          <t>700179708</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>501140687</t>
+          <t>501158583</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>700158115</t>
+          <t>700180725</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>501137980</t>
+          <t>501159620</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>700158791</t>
+          <t>700172574</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>501138635</t>
+          <t>501151689</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>700177109</t>
+          <t>700177003</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>501156014</t>
+          <t>501155898</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>700165716</t>
+          <t>700177331</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>501144721</t>
+          <t>501156236</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>700156748</t>
+          <t>700167860</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>501136583</t>
+          <t>501146895</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>700174712</t>
+          <t>700176044</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>501153857</t>
+          <t>501155219</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>700175759</t>
+          <t>700178275</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>501154934</t>
+          <t>501157140</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>700180529</t>
+          <t>700162387</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>501159414</t>
+          <t>501142092</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>700178230</t>
+          <t>700178805</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>501157095</t>
+          <t>501157670</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>700176290</t>
+          <t>700160254</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>501155485</t>
+          <t>501139829</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>700178788</t>
+          <t>700167283</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>501157663</t>
+          <t>501146298</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>700179115</t>
+          <t>700180165</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>501157980</t>
+          <t>501159040</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>700158787</t>
+          <t>700161536</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>501138631</t>
+          <t>501141171</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>700173256</t>
+          <t>700179573</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>501152381</t>
+          <t>501158448</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>700174593</t>
+          <t>700176147</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>501153748</t>
+          <t>501155322</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>700161073</t>
+          <t>700162037</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>501140688</t>
+          <t>501141712</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>700177677</t>
+          <t>700157660</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>501156583</t>
+          <t>501137495</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>700179218</t>
+          <t>700175779</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>501158083</t>
+          <t>501154954</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>700165912</t>
+          <t>700178223</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>501144917</t>
+          <t>501157088</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>700177465</t>
+          <t>700177639</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>501156370</t>
+          <t>501156544</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>700176933</t>
+          <t>700172035</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>501155828</t>
+          <t>501151140</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>700180395</t>
+          <t>700175778</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>501159282</t>
+          <t>501154953</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>700176047</t>
+          <t>700178231</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>501155222</t>
+          <t>501157096</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>700177105</t>
+          <t>700180529</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>501156010</t>
+          <t>501159414</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>700167283</t>
+          <t>700177108</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>501146298</t>
+          <t>501156013</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>700178504</t>
+          <t>700177270</t>
         </is>
       </c>
     </row>
@@ -2595,14 +2595,14 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>501157369</t>
+          <t>501156175</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>700156749</t>
+          <t>700179928</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -2629,14 +2629,14 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>501136584</t>
+          <t>501158803</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -2646,14 +2646,14 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>700173543</t>
+          <t>700177916</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -2663,14 +2663,14 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>501152668</t>
+          <t>501156821</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -2680,14 +2680,14 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>700162387</t>
+          <t>700180073</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -2697,14 +2697,14 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>501142092</t>
+          <t>501158938</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -2714,14 +2714,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>700177743</t>
+          <t>700157609</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -2731,14 +2731,14 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>501156648</t>
+          <t>501137444</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -2748,14 +2748,14 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>700179928</t>
+          <t>700177918</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -2765,14 +2765,14 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>501158803</t>
+          <t>501156823</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>700172574</t>
+          <t>700178790</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>501151689</t>
+          <t>501157665</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>700179574</t>
+          <t>700156837</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -2833,14 +2833,14 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>501158449</t>
+          <t>501136682</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>700162384</t>
+          <t>700173797</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>501142089</t>
+          <t>501152922</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>700177681</t>
+          <t>700175793</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>501156586</t>
+          <t>501154958</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>700162385</t>
+          <t>700177303</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>501142090</t>
+          <t>501156208</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -2952,14 +2952,14 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>700178599</t>
+          <t>700172267</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>501157466</t>
+          <t>501151372</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -2986,14 +2986,14 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>700161462</t>
+          <t>700158115</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -3003,14 +3003,14 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>501141077</t>
+          <t>501137980</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -3020,14 +3020,14 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>700077051</t>
+          <t>700180687</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -3037,14 +3037,14 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>501035585</t>
+          <t>501159572</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -3054,14 +3054,14 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>700180725</t>
+          <t>700173796</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -3071,14 +3071,14 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>501159620</t>
+          <t>501152921</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>700175794</t>
+          <t>700179218</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -3105,14 +3105,14 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>501154959</t>
+          <t>501158083</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>700178505</t>
+          <t>700178229</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>501157370</t>
+          <t>501157094</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>700178503</t>
+          <t>700160255</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>501157368</t>
+          <t>501139830</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -3190,14 +3190,14 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>700177307</t>
+          <t>700178600</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>501156212</t>
+          <t>501157467</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -3224,14 +3224,14 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>700175725</t>
+          <t>700176946</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -3241,14 +3241,14 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>501154900</t>
+          <t>501155841</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -3258,14 +3258,14 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>700162037</t>
+          <t>700170082</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -3275,14 +3275,14 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>501141712</t>
+          <t>501149147</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -3292,14 +3292,14 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>700173796</t>
+          <t>700163414</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -3309,14 +3309,14 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>501152921</t>
+          <t>501143369</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>700163413</t>
+          <t>700175758</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>501143368</t>
+          <t>501154933</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>700179268</t>
+          <t>700162038</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>501158133</t>
+          <t>501141713</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -3394,14 +3394,14 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>700167288</t>
+          <t>700172036</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -3411,14 +3411,14 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>501146303</t>
+          <t>501151141</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -3428,14 +3428,14 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>700157673</t>
+          <t>700160396</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>501137508</t>
+          <t>501139971</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -3462,14 +3462,14 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>700156869</t>
+          <t>700179621</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>501136724</t>
+          <t>501158496</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -3496,14 +3496,14 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>700178274</t>
+          <t>700161537</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -3513,14 +3513,14 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>501157139</t>
+          <t>501141172</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -3530,14 +3530,14 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>700179117</t>
+          <t>700177322</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -3547,14 +3547,14 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>501157982</t>
+          <t>501156227</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>700160255</t>
+          <t>700161070</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -3581,14 +3581,14 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>501139830</t>
+          <t>501140685</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -3598,14 +3598,14 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>700178579</t>
+          <t>700178131</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -3615,14 +3615,14 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>501157444</t>
+          <t>501156996</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -3632,14 +3632,14 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>700179926</t>
+          <t>700177005</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -3649,14 +3649,14 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>501158801</t>
+          <t>501155900</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>700180687</t>
+          <t>700162521</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -3683,14 +3683,14 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>501159572</t>
+          <t>501142226</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -3700,14 +3700,14 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>700177310</t>
+          <t>700165716</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>501156215</t>
+          <t>501144721</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -3734,14 +3734,14 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>700175163</t>
+          <t>700177743</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>501154328</t>
+          <t>501156648</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>700156836</t>
+          <t>700160292</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>501136681</t>
+          <t>501139867</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>700165633</t>
+          <t>700174411</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>501144628</t>
+          <t>501153556</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -3836,14 +3836,14 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>700176011</t>
+          <t>700175726</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -3853,14 +3853,14 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>501155186</t>
+          <t>501154901</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -3870,14 +3870,14 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>700177321</t>
+          <t>700174410</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -3887,14 +3887,14 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>501156226</t>
+          <t>501153555</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -3904,14 +3904,14 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>700169346</t>
+          <t>700179114</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>501148401</t>
+          <t>501157979</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>700172267</t>
+          <t>700167862</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>501151372</t>
+          <t>501146897</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>700177731</t>
+          <t>700177681</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -3989,14 +3989,14 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>501156636</t>
+          <t>501156586</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -4006,14 +4006,14 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>700177004</t>
+          <t>700176148</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>501155899</t>
+          <t>501155323</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -4040,14 +4040,14 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>700172268</t>
+          <t>700177721</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>501151373</t>
+          <t>501156626</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -4074,14 +4074,14 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>700179923</t>
+          <t>700177307</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -4091,14 +4091,14 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>501158798</t>
+          <t>501156212</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -4108,14 +4108,14 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>700180731</t>
+          <t>700177465</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -4125,14 +4125,14 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>501159626</t>
+          <t>501156370</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -4149,7 +4149,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -4176,14 +4176,14 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>700177638</t>
+          <t>700158791</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -4193,14 +4193,14 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>501156543</t>
+          <t>501138635</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -4210,14 +4210,14 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>700178789</t>
+          <t>700157662</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -4227,14 +4227,14 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>501157664</t>
+          <t>501137497</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -4244,14 +4244,14 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>700162386</t>
+          <t>700166081</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>501142091</t>
+          <t>501145086</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>700165715</t>
+          <t>700161493</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -4295,14 +4295,14 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>501144720</t>
+          <t>501141108</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>700180686</t>
+          <t>700167282</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -4329,14 +4329,14 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>501159571</t>
+          <t>501146297</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>700157662</t>
+          <t>700165715</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -4363,14 +4363,14 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>501137497</t>
+          <t>501144720</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>700173255</t>
+          <t>700174723</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>501152380</t>
+          <t>501153878</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -4414,14 +4414,14 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>700176043</t>
+          <t>700178579</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -4431,14 +4431,14 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>501155218</t>
+          <t>501157444</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>700180530</t>
+          <t>700167857</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -4465,14 +4465,14 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>501159415</t>
+          <t>501146892</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -4482,14 +4482,14 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>700160396</t>
+          <t>700176290</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
@@ -4499,14 +4499,14 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>501139971</t>
+          <t>501155485</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -4516,14 +4516,14 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>700176044</t>
+          <t>700160293</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>501155219</t>
+          <t>501139868</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -4550,14 +4550,14 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>700179925</t>
+          <t>700172573</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>501158800</t>
+          <t>501151688</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -4584,14 +4584,14 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>700174384</t>
+          <t>700176145</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>501153529</t>
+          <t>501155320</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>700177005</t>
+          <t>700176043</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>501155900</t>
+          <t>501155218</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -4652,14 +4652,14 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>700162041</t>
+          <t>700159804</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
@@ -4669,14 +4669,14 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>501141716</t>
+          <t>501139679</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
@@ -4686,14 +4686,14 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>700162038</t>
+          <t>700174572</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
@@ -4703,14 +4703,14 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>501141713</t>
+          <t>501153727</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>700177360</t>
+          <t>700180166</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>501156265</t>
+          <t>501159041</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>700158789</t>
+          <t>700180528</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>501138633</t>
+          <t>501159413</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
@@ -4788,14 +4788,14 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>700176046</t>
+          <t>700177722</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>501155221</t>
+          <t>501156627</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>700180030</t>
+          <t>700176144</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
@@ -4839,14 +4839,14 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>501158905</t>
+          <t>501155319</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
@@ -4856,14 +4856,14 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>700170082</t>
+          <t>700175163</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>501149147</t>
+          <t>501154328</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -4890,14 +4890,14 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>700163414</t>
+          <t>700166080</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>501143369</t>
+          <t>501145085</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
@@ -4924,14 +4924,14 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>700177987</t>
+          <t>700180032</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>501156842</t>
+          <t>501158907</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -4958,14 +4958,14 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>700180041</t>
+          <t>700177895</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
@@ -4975,14 +4975,14 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>501158916</t>
+          <t>501156800</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>700180726</t>
+          <t>700158788</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
@@ -5009,14 +5009,14 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>501159621</t>
+          <t>501138632</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
@@ -5026,14 +5026,14 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>700179911</t>
+          <t>700177310</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
@@ -5043,14 +5043,14 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>501158786</t>
+          <t>501156215</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
@@ -5060,14 +5060,14 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>700172573</t>
+          <t>700178504</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
@@ -5077,14 +5077,14 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>501151688</t>
+          <t>501157369</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -5094,14 +5094,14 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>700178806</t>
+          <t>700172037</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
@@ -5111,14 +5111,14 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>501157671</t>
+          <t>501151142</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
@@ -5128,14 +5128,14 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>700177270</t>
+          <t>700163413</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>501156175</t>
+          <t>501143368</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
@@ -5162,14 +5162,14 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>700160292</t>
+          <t>700174493</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
@@ -5179,14 +5179,14 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>501139867</t>
+          <t>501153638</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
@@ -5196,14 +5196,14 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>700177330</t>
+          <t>700179620</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
@@ -5213,14 +5213,14 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>501156235</t>
+          <t>501158495</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
@@ -5230,14 +5230,14 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>700178687</t>
+          <t>700176947</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
@@ -5247,14 +5247,14 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>501157562</t>
+          <t>501155842</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
@@ -5264,14 +5264,14 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>700168419</t>
+          <t>700179924</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
@@ -5281,14 +5281,14 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>501147464</t>
+          <t>501158799</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>700077050</t>
+          <t>700173236</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
@@ -5315,14 +5315,14 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>501035584</t>
+          <t>501152361</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
@@ -5332,14 +5332,14 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>700175758</t>
+          <t>700178788</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>501154933</t>
+          <t>501157663</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
@@ -5366,14 +5366,14 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>700177896</t>
+          <t>700167859</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
@@ -5383,14 +5383,14 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>501156801</t>
+          <t>501146894</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
@@ -5400,14 +5400,14 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>700174411</t>
+          <t>700174725</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>501153556</t>
+          <t>501153880</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
@@ -5434,14 +5434,14 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>700173849</t>
+          <t>700180152</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
@@ -5451,14 +5451,14 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>501152974</t>
+          <t>501159017</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>700176947</t>
+          <t>700177673</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
@@ -5485,14 +5485,14 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>501155842</t>
+          <t>501156578</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
@@ -5502,14 +5502,14 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>700176148</t>
+          <t>700175777</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>501155323</t>
+          <t>501154952</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>700163189</t>
+          <t>700170081</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>501143134</t>
+          <t>501149146</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
@@ -5570,14 +5570,14 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>700178790</t>
+          <t>700177321</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>501157665</t>
+          <t>501156226</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>700177675</t>
+          <t>700177360</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
@@ -5621,14 +5621,14 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>501156580</t>
+          <t>501156265</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
@@ -5638,14 +5638,14 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>700177918</t>
+          <t>700176047</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
@@ -5655,14 +5655,14 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>501156823</t>
+          <t>501155222</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
@@ -5672,14 +5672,14 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>700177308</t>
+          <t>700170993</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>501156213</t>
+          <t>501150078</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
@@ -5706,14 +5706,14 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>700172035</t>
+          <t>700177110</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
@@ -5723,14 +5723,14 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>501151140</t>
+          <t>501156015</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
@@ -5740,14 +5740,14 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>700178229</t>
+          <t>700180074</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
@@ -5757,14 +5757,14 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>501157094</t>
+          <t>501158939</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
@@ -5774,14 +5774,14 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>700161070</t>
+          <t>700180731</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>501140685</t>
+          <t>501159626</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
@@ -5808,14 +5808,14 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>700166266</t>
+          <t>700178505</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>501145261</t>
+          <t>501157370</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
@@ -5842,14 +5842,14 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>700177464</t>
+          <t>700180909</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
@@ -5859,14 +5859,14 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>501156369</t>
+          <t>501159804</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>700172036</t>
+          <t>700180726</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
@@ -5893,14 +5893,14 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>501151141</t>
+          <t>501159621</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
@@ -5910,14 +5910,14 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>700160293</t>
+          <t>700177070</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
@@ -5927,14 +5927,14 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>501139868</t>
+          <t>501155988</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
@@ -5944,14 +5944,14 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>700167136</t>
+          <t>700165632</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>501146141</t>
+          <t>501144627</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>700174410</t>
+          <t>700170982</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -5995,14 +5995,14 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>501153555</t>
+          <t>501150067</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -6012,14 +6012,14 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>700177110</t>
+          <t>700179116</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
@@ -6029,14 +6029,14 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>501156015</t>
+          <t>501157981</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
@@ -6046,14 +6046,14 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>700169347</t>
+          <t>700174724</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>501148402</t>
+          <t>501153879</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
@@ -6080,14 +6080,14 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>700179573</t>
+          <t>700177731</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -6097,14 +6097,14 @@
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>501158448</t>
+          <t>501156636</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
@@ -6114,14 +6114,14 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>700170993</t>
+          <t>700161494</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>501150078</t>
+          <t>501141109</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
@@ -6148,14 +6148,14 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>700180033</t>
+          <t>700157608</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
@@ -6165,14 +6165,14 @@
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>501158908</t>
+          <t>501137443</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>700161071</t>
+          <t>700177677</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
@@ -6199,14 +6199,14 @@
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>501140686</t>
+          <t>501156583</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
@@ -6216,14 +6216,14 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>700156870</t>
+          <t>700180908</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>501136725</t>
+          <t>501159803</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
@@ -6250,14 +6250,14 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>700178231</t>
+          <t>700177306</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -6267,14 +6267,14 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>501157096</t>
+          <t>501156211</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -6284,14 +6284,14 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>700176118</t>
+          <t>700178232</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>501155293</t>
+          <t>501157097</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -6318,14 +6318,14 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>700158786</t>
+          <t>700180033</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -6335,14 +6335,14 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>501138630</t>
+          <t>501158908</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -6352,14 +6352,14 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>700179116</t>
+          <t>700176012</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -6369,14 +6369,14 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>501157981</t>
+          <t>501155187</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -6386,14 +6386,14 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>700161535</t>
+          <t>700177730</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -6403,14 +6403,14 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>501141170</t>
+          <t>501156635</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>700172270</t>
+          <t>700165912</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>501151375</t>
+          <t>501144917</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -6454,14 +6454,14 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>700178805</t>
+          <t>700161535</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -6471,14 +6471,14 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>501157670</t>
+          <t>501141170</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>700175777</t>
+          <t>700174494</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -6505,14 +6505,14 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>501154952</t>
+          <t>501153639</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>700178232</t>
+          <t>700177896</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -6539,14 +6539,14 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>501157097</t>
+          <t>501156801</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>700170514</t>
+          <t>700180596</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -6573,14 +6573,14 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>501149589</t>
+          <t>501159491</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -6590,14 +6590,14 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>700178787</t>
+          <t>700177986</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -6607,14 +6607,14 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>501157662</t>
+          <t>501156841</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>700177915</t>
+          <t>700161071</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -6641,14 +6641,14 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>501156820</t>
+          <t>501140686</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -6658,14 +6658,14 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>700177680</t>
+          <t>700172271</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -6675,14 +6675,14 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>501156585</t>
+          <t>501151376</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -6692,14 +6692,14 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>700176144</t>
+          <t>700177902</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -6709,14 +6709,14 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>501155319</t>
+          <t>501156807</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -6726,14 +6726,14 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>700177902</t>
+          <t>700165633</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -6743,14 +6743,14 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>501156807</t>
+          <t>501144628</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -6760,14 +6760,14 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>700177727</t>
+          <t>700176011</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>501156632</t>
+          <t>501155186</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -6794,14 +6794,14 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>700174723</t>
+          <t>700178578</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -6811,14 +6811,14 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>501153878</t>
+          <t>501157443</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -6828,14 +6828,14 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>700166265</t>
+          <t>700173849</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>501145260</t>
+          <t>501152974</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
@@ -6862,14 +6862,14 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>700177916</t>
+          <t>700177004</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
@@ -6879,14 +6879,14 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>501156821</t>
+          <t>501155899</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
@@ -6896,14 +6896,14 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>700174725</t>
+          <t>700178787</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
@@ -6913,14 +6913,14 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>501153880</t>
+          <t>501157662</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -6930,14 +6930,14 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>700175793</t>
+          <t>700162384</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -6947,14 +6947,14 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>501154958</t>
+          <t>501142089</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
@@ -6964,14 +6964,14 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>700168420</t>
+          <t>700177917</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>501147465</t>
+          <t>501156822</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
@@ -6998,14 +6998,14 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>700177106</t>
+          <t>700167858</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
@@ -7015,14 +7015,14 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>501156011</t>
+          <t>501146893</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -7032,14 +7032,14 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>700179114</t>
+          <t>700180030</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>501157979</t>
+          <t>501158905</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -7066,14 +7066,14 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>700174724</t>
+          <t>700178224</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -7083,14 +7083,14 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>501153879</t>
+          <t>501157089</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>700177730</t>
+          <t>700162040</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -7117,14 +7117,14 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>501156635</t>
+          <t>501141715</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>700177311</t>
+          <t>700178492</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -7151,14 +7151,14 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>501156216</t>
+          <t>501157357</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -7168,14 +7168,14 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>700177986</t>
+          <t>700177109</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -7185,14 +7185,14 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>501156841</t>
+          <t>501156014</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>700179263</t>
+          <t>700179923</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -7219,14 +7219,14 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>501158128</t>
+          <t>501158798</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -7236,14 +7236,14 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>700177322</t>
+          <t>700177330</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
@@ -7253,14 +7253,14 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>501156227</t>
+          <t>501156235</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>700177306</t>
+          <t>700177915</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -7287,14 +7287,14 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>501156211</t>
+          <t>501156820</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -7304,14 +7304,14 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>700175778</t>
+          <t>700177309</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>501154953</t>
+          <t>501156214</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -7338,14 +7338,14 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>700177107</t>
+          <t>700175759</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>501156012</t>
+          <t>501154934</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
@@ -7372,14 +7372,14 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>700161534</t>
+          <t>700177729</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>501141169</t>
+          <t>501156634</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
@@ -7406,14 +7406,14 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>700177642</t>
+          <t>700178688</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
@@ -7423,14 +7423,14 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>501156547</t>
+          <t>501157563</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -7440,14 +7440,14 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>700156837</t>
+          <t>700173543</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -7457,14 +7457,14 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>501136682</t>
+          <t>501152668</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -7474,14 +7474,14 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>700173236</t>
+          <t>700174383</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -7491,14 +7491,14 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>501152361</t>
+          <t>501153528</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -7508,14 +7508,14 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>700174494</t>
+          <t>700176289</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>501153639</t>
+          <t>501155484</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>700166081</t>
+          <t>700174384</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -7559,14 +7559,14 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>501145086</t>
+          <t>501153529</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -7576,14 +7576,14 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>700173850</t>
+          <t>700162385</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>501152975</t>
+          <t>501142090</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -7610,14 +7610,14 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>700178688</t>
+          <t>700177987</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -7627,14 +7627,14 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>501157563</t>
+          <t>501156842</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -7644,14 +7644,14 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>700175760</t>
+          <t>700175781</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -7661,14 +7661,14 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>501154935</t>
+          <t>501154956</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -7678,14 +7678,14 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>700177003</t>
+          <t>700179112</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>501155898</t>
+          <t>501157977</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -7712,14 +7712,14 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>700159805</t>
+          <t>700180163</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -7729,14 +7729,14 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>501139680</t>
+          <t>501159038</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -7746,14 +7746,14 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>700177639</t>
+          <t>700179926</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -7763,14 +7763,14 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>501156544</t>
+          <t>501158801</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -7780,14 +7780,14 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>700157674</t>
+          <t>700180041</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -7797,14 +7797,14 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>501137509</t>
+          <t>501158916</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -7814,14 +7814,14 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>700161537</t>
+          <t>700168419</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -7831,14 +7831,14 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>501141172</t>
+          <t>501147464</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -7848,14 +7848,14 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>700178275</t>
+          <t>700179545</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>501157140</t>
+          <t>501158420</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -7882,14 +7882,14 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>700162521</t>
+          <t>700178274</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -7899,14 +7899,14 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>501142226</t>
+          <t>501157139</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -7916,14 +7916,14 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>700165632</t>
+          <t>700177271</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>501144627</t>
+          <t>501156176</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -7950,14 +7950,14 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>700177108</t>
+          <t>700177728</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>501156013</t>
+          <t>501156633</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -7984,14 +7984,14 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>700177070</t>
+          <t>700177638</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -8001,14 +8001,14 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>501155988</t>
+          <t>501156543</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -8018,14 +8018,14 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>700175726</t>
+          <t>700180527</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>501154901</t>
+          <t>501159412</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -8052,14 +8052,14 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>700177729</t>
+          <t>700177304</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>501156634</t>
+          <t>501156209</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -8086,14 +8086,14 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>700174383</t>
+          <t>700176046</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -8103,14 +8103,14 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>501153528</t>
+          <t>501155221</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -8120,14 +8120,14 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>700177331</t>
+          <t>700178230</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -8137,14 +8137,14 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>501156236</t>
+          <t>501157095</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -8154,14 +8154,14 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>700179621</t>
+          <t>700157661</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
@@ -8171,14 +8171,14 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>501158496</t>
+          <t>501137496</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
@@ -8188,14 +8188,14 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>700179924</t>
+          <t>700177308</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
@@ -8205,14 +8205,14 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>501158799</t>
+          <t>501156213</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
@@ -8222,14 +8222,14 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>700177726</t>
+          <t>700179117</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>501156631</t>
+          <t>501157982</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
@@ -8256,14 +8256,14 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>700177303</t>
+          <t>700172270</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
@@ -8273,14 +8273,14 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>501156208</t>
+          <t>501151375</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
@@ -8290,14 +8290,14 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>700176946</t>
+          <t>700159761</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
@@ -8307,14 +8307,14 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>501155841</t>
+          <t>501139673</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
@@ -8324,14 +8324,14 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>700180073</t>
+          <t>700162386</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
@@ -8341,14 +8341,14 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>501158938</t>
+          <t>501142091</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
@@ -8358,14 +8358,14 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>700177684</t>
+          <t>700178599</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>501156589</t>
+          <t>501157466</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
@@ -8392,14 +8392,14 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>700178224</t>
+          <t>700158787</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>501157089</t>
+          <t>501138631</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -8426,14 +8426,14 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>700179912</t>
+          <t>700177684</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
@@ -8443,14 +8443,14 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>501158787</t>
+          <t>501156589</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
@@ -8460,14 +8460,14 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>700178223</t>
+          <t>700159805</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
@@ -8477,14 +8477,14 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>501157088</t>
+          <t>501139680</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
@@ -8494,14 +8494,14 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>700179929</t>
+          <t>700175794</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
@@ -8511,14 +8511,14 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>501158804</t>
+          <t>501154959</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -8528,14 +8528,14 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>700177721</t>
+          <t>700156870</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -8545,14 +8545,14 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>501156626</t>
+          <t>501136725</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>700178578</t>
+          <t>700177727</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -8579,14 +8579,14 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>501157443</t>
+          <t>501156632</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -8596,14 +8596,14 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>700161536</t>
+          <t>700180042</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -8613,14 +8613,14 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>501141171</t>
+          <t>501158917</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -8630,14 +8630,14 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>700177069</t>
+          <t>700176118</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -8647,14 +8647,14 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>501155967</t>
+          <t>501155293</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -8664,14 +8664,14 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>700177903</t>
+          <t>700173255</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -8681,14 +8681,14 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>501156808</t>
+          <t>501152380</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -8698,14 +8698,14 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>700173532</t>
+          <t>700178708</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -8715,14 +8715,14 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>501152667</t>
+          <t>501157573</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -8732,14 +8732,14 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>700157609</t>
+          <t>700179912</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -8749,14 +8749,14 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>501137444</t>
+          <t>501158787</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -8766,14 +8766,14 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>700174493</t>
+          <t>700177726</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -8783,14 +8783,14 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>501153638</t>
+          <t>501156631</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -8800,14 +8800,14 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>700166080</t>
+          <t>700180686</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -8817,14 +8817,14 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>501145085</t>
+          <t>501159571</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>700177917</t>
+          <t>700177675</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -8851,14 +8851,14 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>501156822</t>
+          <t>501156580</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -8868,14 +8868,14 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>700179708</t>
+          <t>700179268</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -8885,14 +8885,14 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>501158583</t>
+          <t>501158133</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -8902,14 +8902,14 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>700178131</t>
+          <t>700178503</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -8919,14 +8919,14 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>501156996</t>
+          <t>501157368</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -8936,14 +8936,14 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>700161493</t>
+          <t>700179925</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>501141108</t>
+          <t>501158800</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -8970,14 +8970,14 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>700180596</t>
+          <t>700167288</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -8987,14 +8987,14 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>501159491</t>
+          <t>501146303</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>700177673</t>
+          <t>700175776</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>53073989</t>
+          <t>53078339</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>501156578</t>
+          <t>501154951</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>700172037</t>
+          <t>700179911</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>501151142</t>
+          <t>501158786</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>700176145</t>
+          <t>700167289</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>501155320</t>
+          <t>501146304</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>700175779</t>
+          <t>700177642</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>501154954</t>
+          <t>501156547</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>700179264</t>
+          <t>700179115</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>501158129</t>
+          <t>501157980</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>700167282</t>
+          <t>700158116</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>501146297</t>
+          <t>501137981</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>700180042</t>
+          <t>700179263</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>501158917</t>
+          <t>501158128</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>700177728</t>
+          <t>700077050</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>501156633</t>
+          <t>501035584</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>700159761</t>
+          <t>700158786</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>501139673</t>
+          <t>501138630</t>
         </is>
       </c>
     </row>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>700158116</t>
+          <t>700178130</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>501137981</t>
+          <t>501156995</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>700172038</t>
+          <t>700179533</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>501151143</t>
+          <t>501158408</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>700175761</t>
+          <t>700156869</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>501154936</t>
+          <t>501136724</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>700177895</t>
+          <t>700174593</t>
         </is>
       </c>
     </row>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>501156800</t>
+          <t>501153748</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>700158121</t>
+          <t>700178789</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>501137986</t>
+          <t>501157664</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>700175781</t>
+          <t>700156748</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>501154956</t>
+          <t>501136583</t>
         </is>
       </c>
     </row>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>700178600</t>
+          <t>700156749</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>501157467</t>
+          <t>501136584</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>700180032</t>
+          <t>700180395</t>
         </is>
       </c>
     </row>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>501158907</t>
+          <t>501159282</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>700179620</t>
+          <t>700174712</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>501158495</t>
+          <t>501153857</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>700162040</t>
+          <t>700162041</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,415 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>501141715</t>
+          <t>501141716</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>700177002</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>501155897</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>700178806</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>501157671</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>700179574</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>501158449</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>700177311</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>501156216</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>700167861</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>501146896</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>700173850</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>501152975</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>700169346</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>501148401</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>700176117</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>501155292</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>700180031</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>501158906</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>700163189</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>501143134</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>700172038</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>501151143</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>700179264</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>53078339</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>501158129</t>
         </is>
       </c>
     </row>
